--- a/docs/tables/Various.xlsx
+++ b/docs/tables/Various.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cassidy.peterson\Documents\Github\mahiMSE\docs\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\mahiMSE\docs\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC265F11-20FE-47B9-B0E5-B2FB1B58572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E743AF2D-B5B8-42B9-B3E7-27DB01C97C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4665" yWindow="900" windowWidth="15330" windowHeight="10770" tabRatio="827" firstSheet="13" activeTab="18" xr2:uid="{EE4263A2-8FC9-4695-B2B5-F7B8177F316B}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="827" firstSheet="5" activeTab="6" xr2:uid="{EE4263A2-8FC9-4695-B2B5-F7B8177F316B}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDo" sheetId="15" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="CMO" sheetId="7" r:id="rId3"/>
     <sheet name="RefGrid" sheetId="1" r:id="rId4"/>
     <sheet name="Reference" sheetId="14" r:id="rId5"/>
-    <sheet name="RCM_LHF" sheetId="17" r:id="rId6"/>
-    <sheet name="RCM_config" sheetId="18" r:id="rId7"/>
-    <sheet name="RCM_params" sheetId="19" r:id="rId8"/>
-    <sheet name="Robustness" sheetId="8" r:id="rId9"/>
-    <sheet name="StatQuo" sheetId="20" r:id="rId10"/>
-    <sheet name="Solutions" sheetId="6" r:id="rId11"/>
-    <sheet name="PastData" sheetId="2" r:id="rId12"/>
-    <sheet name="Fleets" sheetId="3" r:id="rId13"/>
+    <sheet name="Fleets" sheetId="3" r:id="rId6"/>
+    <sheet name="PastData" sheetId="2" r:id="rId7"/>
+    <sheet name="RCM_LHF" sheetId="17" r:id="rId8"/>
+    <sheet name="RCM_config" sheetId="18" r:id="rId9"/>
+    <sheet name="RCM_params" sheetId="19" r:id="rId10"/>
+    <sheet name="Robustness" sheetId="8" r:id="rId11"/>
+    <sheet name="StatQuo" sheetId="20" r:id="rId12"/>
+    <sheet name="Solutions" sheetId="6" r:id="rId13"/>
     <sheet name="Data_Assump" sheetId="9" r:id="rId14"/>
     <sheet name="Areas" sheetId="4" r:id="rId15"/>
     <sheet name="PMs" sheetId="10" r:id="rId16"/>
@@ -48,15 +48,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="353">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -118,12 +115,6 @@
     <t>Intl</t>
   </si>
   <si>
-    <t>Disc</t>
-  </si>
-  <si>
-    <t>UnRep</t>
-  </si>
-  <si>
     <t>Recreational North</t>
   </si>
   <si>
@@ -139,12 +130,6 @@
     <t>International</t>
   </si>
   <si>
-    <t>Discard</t>
-  </si>
-  <si>
-    <t>Unreported</t>
-  </si>
-  <si>
     <t>Areas</t>
   </si>
   <si>
@@ -517,9 +502,6 @@
     <t>""</t>
   </si>
   <si>
-    <t>Indices</t>
-  </si>
-  <si>
     <t>CAR+FLK</t>
   </si>
   <si>
@@ -550,9 +532,6 @@
     <t>NOAA dataset</t>
   </si>
   <si>
-    <t>Derived from a custom 5-area VAST model fitted to U.S. pelagic longline catch and effort data</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOAA dataset, data are sparse for the International fleet and not used. Not avialable for unreported and discard fleets. </t>
   </si>
   <si>
@@ -562,9 +541,6 @@
     <t>CAR+FLK, NCFL</t>
   </si>
   <si>
-    <t>CAR+FLK, NCA, NNC+VBM</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -1093,12 +1069,6 @@
     <t>Make robustness slick or add to existing</t>
   </si>
   <si>
-    <t xml:space="preserve">Based on FAO database. Assumed to have the same seasonal distribution as the USCom fleet. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on Sea Around Us database. Assumed to have the same seasonal distribution as the USCom fleet. </t>
-  </si>
-  <si>
     <t>Regionally mixed on willing to accept more restrictions</t>
   </si>
   <si>
@@ -1126,13 +1096,22 @@
     <t>Wilmington to Maine</t>
   </si>
   <si>
-    <t>USA commercial landings</t>
-  </si>
-  <si>
-    <t>All US commercial landings (pelagic longline gear and other gear types)</t>
-  </si>
-  <si>
     <t>von Bertalanffy asymptotic length, L-infinity (male and female combined) (mm)</t>
+  </si>
+  <si>
+    <t>Based on FAO database. Assumed to have the same seasonal distribution as the USCom fleet, including unreported catches</t>
+  </si>
+  <si>
+    <t>All US commercial landings (pelagic longline gear and other gear types), including dead discards</t>
+  </si>
+  <si>
+    <t>USA commercial</t>
+  </si>
+  <si>
+    <t>Spatial Indices</t>
+  </si>
+  <si>
+    <t>Derived from either (1) a  5-area VAST model  or a (2) a 5-area generalized linear model, both fitted to U.S. pelagic longline catch and effort data</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1180,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1212,10 +1191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1235,9 +1211,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1275,7 +1251,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1381,7 +1357,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1523,7 +1499,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1532,61 +1508,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A2B60A-BF4A-49C5-86BC-AAE256712F35}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.1796875" customWidth="1"/>
+    <col min="2" max="2" width="39.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>336</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>343</v>
-      </c>
-      <c r="B6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
     </row>
   </sheetData>
@@ -1595,52 +1571,113 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87EF8B3-71A2-42AA-ACE0-0FF455C3A4FB}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDCC00A-806A-4ED8-9F4D-5FFC556579AD}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="76.26953125" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" t="s">
         <v>324</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D4">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>326</v>
+      </c>
+      <c r="C5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7">
+        <f>SUM(D2:D6)</f>
+        <v>1288</v>
       </c>
     </row>
   </sheetData>
@@ -1649,33 +1686,199 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EAC486-A017-463D-8ADB-61E4EC63F3EE}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE8661-58F7-4A4D-9F7C-724104DE0CE4}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="59.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="B4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>210</v>
+      </c>
+      <c r="B5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" t="s">
+        <v>302</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C11" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" t="s">
+        <v>303</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" t="s">
+        <v>303</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -1684,68 +1887,52 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081D8FC8-91C1-41A2-9BA3-CA12A708DF6A}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87EF8B3-71A2-42AA-ACE0-0FF455C3A4FB}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>317</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>309</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>316</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>315</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>313</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>165</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -1754,195 +1941,33 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A566BA38-7908-4D5C-90BF-A498D09C814B}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="42.140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EAC486-A017-463D-8ADB-61E4EC63F3EE}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>346</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1953,66 +1978,66 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9B310C-599A-4BAB-B51A-E74D7F51AC0B}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="53.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>77</v>
       </c>
-      <c r="B2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>78</v>
       </c>
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" t="s">
         <v>79</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>330</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2023,76 +2048,76 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5657926F-43CB-455A-AC6E-4954BADA8C82}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
         <v>155</v>
       </c>
-      <c r="C2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
         <v>156</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2103,151 +2128,151 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47864489-C592-46C6-B98F-008C606ED044}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D10" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2258,50 +2283,50 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26CB1A4-32CC-40D1-B203-9F91BD896760}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="41.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
         <v>104</v>
-      </c>
-      <c r="B3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2312,82 +2337,82 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97162EB3-8C36-45A6-A7F5-E11890F2B3BC}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="105.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="105.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>110</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>112</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>114</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>118</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>120</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2398,203 +2423,203 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06522138-93B3-4409-93D1-7697414686F5}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="75.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="5" width="42.85546875" customWidth="1"/>
+    <col min="1" max="1" width="75.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B2">
         <v>1.27</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D2">
         <v>0.08</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B3">
         <v>1289</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D3">
         <v>0.02</v>
       </c>
       <c r="E3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B5">
         <v>458</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B6">
         <v>0.15</v>
       </c>
       <c r="C6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" t="s">
         <v>233</v>
       </c>
-      <c r="D6" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" t="s">
-        <v>233</v>
-      </c>
-      <c r="D7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B8">
         <v>2.67</v>
       </c>
       <c r="C8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" t="s">
         <v>233</v>
       </c>
-      <c r="D8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D9">
         <v>0.1</v>
       </c>
       <c r="E9" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="E10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B11">
         <v>0.25</v>
       </c>
       <c r="C11" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -2604,44 +2629,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9680D609-91F9-4C15-AAA9-F73651BACC8D}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2652,122 +2677,122 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70822580-D34B-4110-AF41-EF4D8F8C8CF2}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
     <col min="2" max="2" width="87" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="5" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="7" spans="1:2" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="8" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="9" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="10" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="11" spans="1:2" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="12" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="13" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="14" spans="1:2" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2778,61 +2803,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E084CD2-D73D-4BCF-9E66-EB835B19C48C}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>56</v>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2843,12 +2868,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D0E3CA-ADCA-4689-A286-6277FDD311C5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="22.5703125" customWidth="1"/>
+    <col min="1" max="3" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2859,18 +2884,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2881,37 +2906,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2922,31 +2947,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5914CF4D-5333-407A-A26F-9917FF960A73}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B2">
         <v>0.25</v>
@@ -2964,9 +2989,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -2984,9 +3009,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B4">
         <v>0.25</v>
@@ -3004,9 +3029,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B5">
         <v>0.5</v>
@@ -3024,9 +3049,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B6">
         <v>0.25</v>
@@ -3044,9 +3069,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -3064,9 +3089,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B8">
         <v>0.25</v>
@@ -3084,9 +3109,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B9">
         <v>0.5</v>
@@ -3104,9 +3129,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B10">
         <v>0.25</v>
@@ -3124,9 +3149,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -3144,9 +3169,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B12">
         <v>0.25</v>
@@ -3164,9 +3189,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B13">
         <v>0.5</v>
@@ -3184,9 +3209,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B14">
         <v>0.25</v>
@@ -3204,9 +3229,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B15">
         <v>0.5</v>
@@ -3224,9 +3249,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B16">
         <v>0.25</v>
@@ -3244,9 +3269,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B17">
         <v>0.5</v>
@@ -3264,9 +3289,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B18">
         <v>0.25</v>
@@ -3284,9 +3309,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B19">
         <v>0.5</v>
@@ -3304,9 +3329,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B20">
         <v>0.25</v>
@@ -3324,9 +3349,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B21">
         <v>0.5</v>
@@ -3344,9 +3369,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B22">
         <v>0.25</v>
@@ -3364,9 +3389,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B23">
         <v>0.5</v>
@@ -3384,9 +3409,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B24">
         <v>0.25</v>
@@ -3404,9 +3429,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B25">
         <v>0.5</v>
@@ -3424,9 +3449,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B26">
         <v>0.25</v>
@@ -3444,9 +3469,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B27">
         <v>0.5</v>
@@ -3464,9 +3489,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B28">
         <v>0.25</v>
@@ -3484,9 +3509,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B29">
         <v>0.5</v>
@@ -3504,9 +3529,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B30">
         <v>0.25</v>
@@ -3524,9 +3549,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B31">
         <v>0.5</v>
@@ -3544,9 +3569,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B32">
         <v>0.25</v>
@@ -3564,9 +3589,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B33">
         <v>0.5</v>
@@ -3590,79 +3615,155 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D760A6-0824-4E71-80B5-1B4ED9B6FA8E}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A566BA38-7908-4D5C-90BF-A498D09C814B}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="6" max="6" width="42.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>257</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>258</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>350</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>262</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>266</v>
+        <v>161</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -3671,108 +3772,68 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA40A8BC-C366-49A3-87C6-4B9DEB0D3E33}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081D8FC8-91C1-41A2-9BA3-CA12A708DF6A}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.140625" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="3" max="3" width="29.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>275</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>291</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>298</v>
-      </c>
-      <c r="B10" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>300</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>301</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>302</v>
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -3781,113 +3842,79 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDCC00A-806A-4ED8-9F4D-5FFC556579AD}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D760A6-0824-4E71-80B5-1B4ED9B6FA8E}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="76.28515625" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" customWidth="1"/>
+    <col min="3" max="3" width="37.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" t="s">
         <v>251</v>
       </c>
-      <c r="B1" t="s">
-        <v>331</v>
-      </c>
       <c r="C1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D2">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="B3" t="s">
-        <v>332</v>
+        <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="B4" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D4">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D5">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>224</v>
       </c>
       <c r="C6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D7">
-        <f>SUM(D2:D6)</f>
-        <v>1288</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -3896,199 +3923,108 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE8661-58F7-4A4D-9F7C-724104DE0CE4}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA40A8BC-C366-49A3-87C6-4B9DEB0D3E33}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="3" width="59.140625" customWidth="1"/>
+    <col min="1" max="1" width="51.1796875" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" t="s">
-        <v>309</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B9" t="s">
-        <v>309</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>222</v>
-      </c>
-      <c r="B10" t="s">
-        <v>309</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="B10" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>224</v>
-      </c>
-      <c r="B12" t="s">
-        <v>309</v>
-      </c>
-      <c r="C12" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>225</v>
-      </c>
-      <c r="B13" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>226</v>
-      </c>
-      <c r="B14" t="s">
-        <v>310</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>227</v>
-      </c>
-      <c r="B15" t="s">
-        <v>310</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>304</v>
-      </c>
-      <c r="B16" t="s">
-        <v>311</v>
-      </c>
-      <c r="C16" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>305</v>
-      </c>
-      <c r="B17" t="s">
-        <v>311</v>
-      </c>
-      <c r="C17" t="s">
-        <v>315</v>
+        <v>294</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
